--- a/data/trans_bre/P32B-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P32B-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,43</t>
+          <t>-0,99; 2,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,73; -1,34</t>
+          <t>-5,29; -1,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 0,23</t>
+          <t>-4,69; 0,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 0,76</t>
+          <t>-5,28; 0,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 144,67</t>
+          <t>-100,0; 83,11</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 4,05</t>
+          <t>-0,63; 3,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 4,33</t>
+          <t>-0,4; 4,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 0,77</t>
+          <t>-2,93; 0,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,27</t>
+          <t>0,05; 4,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,0</t>
+          <t>-1,79; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,74; -2,17</t>
+          <t>-6,76; -2,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 11,18</t>
+          <t>-1,9; 10,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,78; -0,76</t>
+          <t>-5,35; -0,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1800,09</t>
+          <t>-100,0; 1194,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,89</t>
+          <t>-1,38; 3,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,69; -1,27</t>
+          <t>-4,73; -1,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,91</t>
+          <t>-2,78; 0,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,06; -0,28</t>
+          <t>-4,16; -0,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 367,29</t>
+          <t>-100,0; 460,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -7,7</t>
+          <t>-100,0; -29,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-87,58; 96,0</t>
+          <t>-87,7; 72,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -9,72</t>
+          <t>-100,0; -12,16</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 4,52</t>
+          <t>-0,42; 4,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,33</t>
+          <t>-2,12; 2,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -0,73</t>
+          <t>-3,83; -0,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 2,3</t>
+          <t>-3,62; 1,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 540,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-83,12; 194,3</t>
+          <t>-81,48; 143,81</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 0,94</t>
+          <t>-2,97; 0,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,04; -1,0</t>
+          <t>-8,86; -1,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 1,52</t>
+          <t>-3,58; 1,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,41</t>
+          <t>0,0; 9,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -0,26</t>
+          <t>-100,0; -17,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,01</t>
+          <t>-0,49; 1,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,2; -1,3</t>
+          <t>-3,24; -1,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; -0,24</t>
+          <t>-1,95; -0,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,34</t>
+          <t>-2,1; 0,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-55,01; 176,85</t>
+          <t>-49,77; 221,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-90,3; -46,8</t>
+          <t>-90,78; -49,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-75,47; -11,77</t>
+          <t>-77,73; -8,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-75,3; 23,93</t>
+          <t>-76,91; 22,62</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32B-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P32B-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,41</t>
+          <t>-1,85</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-54,22%</t>
+          <t>-61,87%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,75</t>
+          <t>-1,28; 2,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,29; -1,22</t>
+          <t>-5,7; -1,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 0,12</t>
+          <t>-4,35; 0,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 0,69</t>
+          <t>-5,08; 0,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 466,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 83,11</t>
+          <t>-100,0; 116,84</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,8</t>
+          <t>2,13</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>428,69%</t>
+          <t>294,26%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 3,77</t>
+          <t>-0,44; 4,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 4,28</t>
+          <t>-0,39; 4,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 0,75</t>
+          <t>-2,96; 0,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 4,98</t>
+          <t>-0,09; 5,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,98</t>
+          <t>-2,75</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,0</t>
+          <t>-1,95; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,76; -2,17</t>
+          <t>-6,58; -2,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 10,31</t>
+          <t>-1,53; 9,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,35; -0,65</t>
+          <t>-7,43; -1,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1194,74</t>
+          <t>-100,0; 1145,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,79</t>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-78,56%</t>
+          <t>-4,45%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,02</t>
+          <t>-1,24; 3,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,73; -1,46</t>
+          <t>-4,76; -1,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,91</t>
+          <t>-2,73; 0,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,16; -0,31</t>
+          <t>-1,74; 3,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 460,5</t>
+          <t>-79,7; 399,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -29,81</t>
+          <t>-100,0; -12,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-87,7; 72,88</t>
+          <t>-85,6; 69,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -12,16</t>
+          <t>-79,45; 404,28</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>-1,29</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-27,56%</t>
+          <t>-40,27%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 4,53</t>
+          <t>-0,42; 4,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,19</t>
+          <t>-2,15; 2,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; -0,88</t>
+          <t>-4,07; -0,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 1,87</t>
+          <t>-4,26; 1,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 540,58</t>
+          <t>-100,0; 410,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,14 +1095,14 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-81,48; 143,81</t>
+          <t>-82,98; 110,31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>1,76</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 0,94</t>
+          <t>-2,98; 0,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,86; -1,31</t>
+          <t>-8,73; -1,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 1,64</t>
+          <t>-3,81; 1,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,39</t>
+          <t>0,0; 9,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -17,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-91,75; 345,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,81</t>
+          <t>-0,4</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-40,5%</t>
+          <t>-18,41%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,12</t>
+          <t>-0,46; 1,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,24; -1,32</t>
+          <t>-3,13; -1,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,95; -0,17</t>
+          <t>-1,99; -0,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,34</t>
+          <t>-1,48; 0,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-49,77; 221,89</t>
+          <t>-48,83; 208,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-90,78; -49,67</t>
+          <t>-90,36; -48,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-77,73; -8,27</t>
+          <t>-75,25; -5,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-76,91; 22,62</t>
+          <t>-56,39; 51,09</t>
         </is>
       </c>
     </row>
